--- a/etf_holdings/2026-09-14_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-14_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.37%364,000</t>
+          <t>8.77%364,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.37%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.27%480,000</t>
+          <t>8.24%480,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.27%</t>
+          <t>8.24%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.82%323,000</t>
+          <t>6.80%323,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.82%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.31%1,720,000</t>
+          <t>6.28%1,720,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>6.28%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>+0.95%5820</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3310</v>
+        <v>5820</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.92%468,000</t>
+          <t>5.70%260,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>5.70%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>468000</v>
+        <v>260000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>+4.27%1955</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5820</v>
+        <v>1955</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.63%260,000</t>
+          <t>4.89%665,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>260000</v>
+        <v>665000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>-1.78%3310</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1955</v>
+        <v>3310</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.68%665,000</t>
+          <t>4.71%378,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>665000</v>
+        <v>378000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.36%1,127,000</t>
+          <t>4.33%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.63%962</t>
+          <t>-0.53%1875</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>962</v>
+        <v>1875</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.82%1,030,000</t>
+          <t>3.73%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1030000</v>
+        <v>529000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-2.63%962</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1875</v>
+        <v>962</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.75%529,000</t>
+          <t>3.73%1,030,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>529000</v>
+        <v>1030000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.65%54,300</t>
+          <t>3.67%54,300</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.20%245,000</t>
+          <t>3.11%245,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.00%739,000</t>
+          <t>2.93%739,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:07</t>
+          <t>2026-09-14 23:58:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.84%120,000</t>
+          <t>2.85%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.19%271,000</t>
+          <t>2.21%271,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.02%1,200,000</t>
+          <t>2.01%1,200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.91%42,000</t>
+          <t>1.90%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,25 +1602,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>-2.15%1365</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2380</v>
+        <v>1365</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.62%179,000</t>
+          <t>1.62%306,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1629,11 +1629,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>179000</v>
+        <v>306000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-1.24%2380</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1365</v>
+        <v>2380</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.57%306,000</t>
+          <t>1.60%179,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>306000</v>
+        <v>179000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.45%150,000</t>
+          <t>1.40%150,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.41%282,000</t>
+          <t>1.31%282,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.29%149,139</t>
+          <t>1.27%149,139</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.94%1,778,000</t>
+          <t>0.95%1,778,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.93%198,000</t>
+          <t>0.91%198,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.21%6600</t>
+          <t>0%1620</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6600</v>
+        <v>1620</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.60%23,000</t>
+          <t>0.57%94,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>23000</v>
+        <v>94000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>-4.21%6600</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.21%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1620</v>
+        <v>6600</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.57%94,000</t>
+          <t>0.57%23,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>94000</v>
+        <v>23000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:19</t>
+          <t>2026-09-14 23:58:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.53%250,000</t>
+          <t>0.51%250,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.34%146,000</t>
+          <t>0.35%146,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>4749新應材</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-5.49%2325</t>
+          <t>-4.76%721</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-4.76%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2325</v>
+        <v>721</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.26%30,000</t>
+          <t>0.25%95,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>30000</v>
+        <v>95000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4749新應材</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.76%721</t>
+          <t>-2.48%157.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.76%</t>
+          <t>-2.48%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>721</v>
+        <v>157.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.26%95,000</t>
+          <t>0.13%211,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>95000</v>
+        <v>211000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>4576大銀微系統</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.48%157.5</t>
+          <t>-5.79%228</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-5.79%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>157.5</v>
+        <v>228</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.12%211,000</t>
+          <t>0.06%72,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>211000</v>
+        <v>72000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4576大銀微系統</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.79%228</t>
+          <t>-0.57%261.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.79%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>228</v>
+        <v>261.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.07%72,000</t>
+          <t>0.04%42,650</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>72000</v>
+        <v>42650</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3163波若威</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>-5.23%670</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>261.5</v>
+        <v>670</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.04%42,650</t>
+          <t>0.03%13,300</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>42650</v>
+        <v>13300</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3163波若威</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-5.23%670</t>
+          <t>-3.96%230.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>670</v>
+        <v>230.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.03%13,300</t>
+          <t>0.03%34,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>13300</v>
+        <v>34000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-3.96%230.5</t>
+          <t>+5.73%442.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>+5.73%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>230.5</v>
+        <v>442.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.03%34,000</t>
+          <t>0.02%10,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>34000</v>
+        <v>10000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+5.73%442.5</t>
+          <t>-1.64%3590</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+5.73%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>442.5</v>
+        <v>3590</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.02%10,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.64%3590</t>
+          <t>-0.59%670</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3590</v>
+        <v>670</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,34 +3066,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.59%670</t>
+          <t>-0.97%612</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>670</v>
+        <v>612</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>&lt;0.01%3,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>+0.63%1590</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>612</v>
+        <v>1590</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%3,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:30</t>
+          <t>2026-09-14 23:58:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.63%1590</t>
+          <t>+4.43%1415</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+4.43%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1590</v>
+        <v>1415</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
